--- a/Class Files/5. Lookup.xlsx
+++ b/Class Files/5. Lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel sheet itvedant\Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FB5A1D-8C2A-413C-A155-9278A942BDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4368DF7-577C-44A8-AB2E-25A921A124BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{80A2D1DF-9025-4F9A-841F-E1BCCFD46CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80A2D1DF-9025-4F9A-841F-E1BCCFD46CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Vlookup" sheetId="1" r:id="rId1"/>
@@ -514,18 +514,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37E5F70-740C-4AA9-BD80-A0DECEE1CDF0}">
   <dimension ref="C5:P25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="10.88671875" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>4</v>
       </c>
@@ -580,7 +586,7 @@
         <v>Bharat G</v>
       </c>
     </row>
-    <row r="7" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>5</v>
       </c>
@@ -605,7 +611,7 @@
         <v>764439</v>
       </c>
     </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>6</v>
       </c>
@@ -619,7 +625,7 @@
         <v>218315.7</v>
       </c>
     </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>7</v>
       </c>
@@ -633,7 +639,7 @@
         <v>219178.125</v>
       </c>
     </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>8</v>
       </c>
@@ -661,7 +667,7 @@
         <v>Santosh B</v>
       </c>
     </row>
-    <row r="11" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>9</v>
       </c>
@@ -684,7 +690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -701,7 +707,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="13" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>11</v>
       </c>
@@ -722,7 +728,7 @@
         <v>Namit J</v>
       </c>
     </row>
-    <row r="14" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>12</v>
       </c>
@@ -743,7 +749,7 @@
         <v>Rakesh B</v>
       </c>
     </row>
-    <row r="15" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>13</v>
       </c>
@@ -772,7 +778,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="16" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>14</v>
       </c>
@@ -790,7 +796,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>15</v>
       </c>
@@ -811,7 +817,7 @@
         <v>Chris G</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>16</v>
       </c>
@@ -825,7 +831,7 @@
         <v>159665.4</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="s">
         <v>0</v>
       </c>
@@ -869,7 +875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C23" s="4" t="s">
         <v>1</v>
       </c>
@@ -913,7 +919,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C24" s="4" t="s">
         <v>3</v>
       </c>
@@ -957,7 +963,7 @@
         <v>709624</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C25" s="4" t="s">
         <v>2</v>
       </c>
@@ -1009,21 +1015,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989FF273-7F53-487F-8180-18C0890221C0}">
   <dimension ref="C2:P13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1111,7 +1117,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1161,7 @@
         <v>709624</v>
       </c>
     </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
@@ -1199,7 +1205,7 @@
         <v>159665.4</v>
       </c>
     </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1223,7 +1229,7 @@
         <v>868450</v>
       </c>
     </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1236,17 +1242,17 @@
         <v>974125</v>
       </c>
     </row>
-    <row r="11" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C11" s="5">
         <v>224226.67500000002</v>
       </c>
     </row>
-    <row r="12" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C12" s="5">
         <v>175071.375</v>
       </c>
     </row>
-    <row r="13" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C13" s="5">
         <v>206941.05000000002</v>
       </c>
